--- a/data/trans_dic/IMC_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,14; 68,56</t>
+          <t>58,56; 68,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,47; 70,1</t>
+          <t>60,25; 70,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,12; 63,97</t>
+          <t>53,88; 64,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,12; 62,82</t>
+          <t>53,77; 63,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,04; 34,65</t>
+          <t>23,39; 34,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 38,2</t>
+          <t>26,91; 38,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,6; 45,96</t>
+          <t>34,38; 45,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,98; 38,62</t>
+          <t>30,48; 38,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,29; 53,06</t>
+          <t>46,34; 53,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,77; 55,43</t>
+          <t>47,8; 55,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,93; 54,45</t>
+          <t>47,04; 54,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,21; 50,15</t>
+          <t>44,19; 50,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,4; 64,73</t>
+          <t>54,39; 65,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,14; 73,26</t>
+          <t>63,08; 72,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,6; 64,85</t>
+          <t>54,19; 64,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,32; 64,59</t>
+          <t>54,75; 64,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,79; 39,87</t>
+          <t>29,83; 39,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,48; 47,8</t>
+          <t>36,6; 48,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,21; 45,65</t>
+          <t>35,45; 46,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,43; 50,09</t>
+          <t>41,31; 50,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,42; 51,48</t>
+          <t>43,6; 50,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,75; 60,5</t>
+          <t>52,48; 60,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,85; 53,79</t>
+          <t>46,3; 53,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,41; 57,5</t>
+          <t>50,35; 57,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,24; 70,2</t>
+          <t>62,68; 70,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,87; 76,23</t>
+          <t>69,16; 76,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,26; 70,05</t>
+          <t>61,32; 69,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,28; 93,46</t>
+          <t>68,02; 93,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,25; 52,71</t>
+          <t>37,52; 52,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,61; 67,14</t>
+          <t>54,34; 67,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,8; 67,02</t>
+          <t>49,84; 66,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,8; 52,31</t>
+          <t>39,4; 52,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,03; 65,51</t>
+          <t>57,71; 64,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,65; 72,1</t>
+          <t>66,08; 72,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,88; 67,57</t>
+          <t>59,48; 67,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,64; 87,85</t>
+          <t>61,57; 90,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,19; 66,75</t>
+          <t>61,4; 66,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,34; 71,21</t>
+          <t>65,29; 71,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,64; 69,62</t>
+          <t>63,87; 69,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,53; 70,86</t>
+          <t>64,14; 71,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,24; 47,99</t>
+          <t>40,69; 47,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,59; 54,23</t>
+          <t>46,96; 54,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,47</t>
+          <t>43,12; 50,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,41; 80,22</t>
+          <t>50,53; 79,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,84; 59,1</t>
+          <t>54,64; 58,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,94; 63,56</t>
+          <t>58,87; 63,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,05; 60,65</t>
+          <t>56,1; 60,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,72; 75,28</t>
+          <t>59,74; 75,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,79; 59,86</t>
+          <t>49,31; 60,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,03; 69,44</t>
+          <t>60,74; 69,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,45; 67,68</t>
+          <t>59,47; 67,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,81; 69,68</t>
+          <t>60,38; 69,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,33; 60,49</t>
+          <t>51,79; 60,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,66; 67,35</t>
+          <t>59,55; 67,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,41; 65,24</t>
+          <t>58,04; 65,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,96; 76,07</t>
+          <t>62,08; 75,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,88; 59,13</t>
+          <t>52,25; 58,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,41; 66,95</t>
+          <t>61,39; 67,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,98; 65,48</t>
+          <t>59,96; 65,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,73; 71,7</t>
+          <t>62,61; 71,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 28,22</t>
+          <t>18,83; 28,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,83; 38,59</t>
+          <t>27,05; 37,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,28; 31,71</t>
+          <t>20,75; 31,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,08; 45,54</t>
+          <t>24,42; 45,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,55; 56,15</t>
+          <t>50,69; 56,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,55; 62,44</t>
+          <t>56,44; 62,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,07; 60,51</t>
+          <t>53,84; 60,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,79; 59,01</t>
+          <t>51,61; 58,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,15; 50,13</t>
+          <t>45,29; 50,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51,37; 56,83</t>
+          <t>51,38; 56,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47,48; 53,23</t>
+          <t>47,57; 53,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,34; 54,01</t>
+          <t>46,21; 54,24</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,51; 61,06</t>
+          <t>57,52; 60,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,87; 67,2</t>
+          <t>63,56; 67,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,92; 62,4</t>
+          <t>59,12; 62,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,67; 73,88</t>
+          <t>61,75; 72,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,62; 48,97</t>
+          <t>45,58; 49,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,5; 55,96</t>
+          <t>52,54; 56,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,46; 53,89</t>
+          <t>50,27; 53,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,94; 64,65</t>
+          <t>51,66; 63,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52,06; 54,42</t>
+          <t>51,95; 54,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58,51; 61,07</t>
+          <t>58,6; 61,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55,12; 57,62</t>
+          <t>55,21; 57,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,33; 65,93</t>
+          <t>57,34; 66,35</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>277654; 321912</t>
+          <t>274944; 319501</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>259958; 301351</t>
+          <t>258991; 300900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>229258; 270950</t>
+          <t>228236; 271260</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269039; 312298</t>
+          <t>267323; 314420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73036; 105283</t>
+          <t>71069; 104645</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83142; 118949</t>
+          <t>83811; 119466</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119542; 154342</t>
+          <t>115461; 153858</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>134934; 168220</t>
+          <t>132778; 167242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>357981; 410365</t>
+          <t>358385; 412802</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>354093; 410906</t>
+          <t>354302; 411332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>356374; 413490</t>
+          <t>357239; 413583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>412306; 467732</t>
+          <t>412115; 470471</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>197010; 234402</t>
+          <t>196978; 235670</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>255121; 296000</t>
+          <t>254872; 294546</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>200133; 237698</t>
+          <t>198634; 237197</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>246988; 288371</t>
+          <t>244441; 289424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>109898; 147096</t>
+          <t>110033; 145232</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>115881; 156115</t>
+          <t>119515; 158534</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127393; 165165</t>
+          <t>128250; 166676</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>155335; 187815</t>
+          <t>154875; 187962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>317424; 376353</t>
+          <t>318730; 370478</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>385403; 442053</t>
+          <t>383399; 442894</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>333965; 391768</t>
+          <t>337230; 391997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>414039; 472281</t>
+          <t>413564; 470709</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>337599; 380776</t>
+          <t>339959; 381907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>426459; 472037</t>
+          <t>428280; 472799</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>308121; 352359</t>
+          <t>308444; 351900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>449992; 615950</t>
+          <t>448283; 614138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61343; 86796</t>
+          <t>61782; 86135</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>133548; 164204</t>
+          <t>132902; 164403</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79226; 104523</t>
+          <t>77726; 103148</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64382; 84631</t>
+          <t>63748; 84241</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>410288; 463201</t>
+          <t>408084; 457678</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>567073; 622786</t>
+          <t>570826; 625554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>394574; 445225</t>
+          <t>391904; 445700</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>505962; 721093</t>
+          <t>505405; 739422</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>750483; 818639</t>
+          <t>753033; 820119</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>746615; 813681</t>
+          <t>745959; 811953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704738; 770968</t>
+          <t>707280; 768034</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645474; 719983</t>
+          <t>651685; 722353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>285411; 340445</t>
+          <t>288633; 339611</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>350788; 408348</t>
+          <t>353599; 407459</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>336262; 395531</t>
+          <t>337887; 394852</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>484426; 770786</t>
+          <t>485503; 764049</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1061676; 1144018</t>
+          <t>1057722; 1141711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1117231; 1204738</t>
+          <t>1115826; 1202303</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1059853; 1146881</t>
+          <t>1060783; 1148266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1180695; 1488256</t>
+          <t>1180980; 1483614</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>166988; 204880</t>
+          <t>168765; 206438</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>301921; 343533</t>
+          <t>300509; 342567</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>349780; 398216</t>
+          <t>349870; 397202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>278458; 324422</t>
+          <t>281125; 325645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>292235; 337811</t>
+          <t>289201; 335224</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>424947; 479751</t>
+          <t>424191; 481025</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>394836; 448635</t>
+          <t>399109; 449060</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>477082; 585799</t>
+          <t>478047; 578319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>467315; 532638</t>
+          <t>470615; 530415</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>741283; 808067</t>
+          <t>740987; 808819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>765311; 835614</t>
+          <t>765137; 831882</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>775148; 885884</t>
+          <t>773626; 886000</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55815; 83655</t>
+          <t>55821; 84794</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71360; 102619</t>
+          <t>71934; 100904</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59062; 88028</t>
+          <t>57593; 88386</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56798; 107413</t>
+          <t>57601; 106324</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>620039; 688787</t>
+          <t>621854; 691812</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>595220; 657242</t>
+          <t>594087; 660510</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>543128; 607787</t>
+          <t>540747; 604880</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>371721; 423485</t>
+          <t>370418; 421614</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>687698; 763522</t>
+          <t>689740; 762516</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>677380; 749278</t>
+          <t>677479; 749979</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608728; 682439</t>
+          <t>609825; 682256</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>441863; 515072</t>
+          <t>440699; 517195</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1862922; 1977920</t>
+          <t>1863126; 1971863</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2143837; 2255582</t>
+          <t>2133197; 2251572</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1924586; 2038297</t>
+          <t>1931062; 2044057</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2047609; 2452833</t>
+          <t>2050258; 2412984</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1520018; 1631708</t>
+          <t>1518579; 1632520</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1785081; 1902975</t>
+          <t>1786480; 1909749</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1680154; 1794296</t>
+          <t>1673720; 1797583</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1776854; 2211758</t>
+          <t>1767122; 2180609</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3420708; 3575929</t>
+          <t>3413555; 3575398</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3953076; 4126117</t>
+          <t>3959546; 4124519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3635846; 3800466</t>
+          <t>3641429; 3800974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3864901; 4444648</t>
+          <t>3865037; 4472569</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,56; 68,05</t>
+          <t>59,32; 68,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,25; 70,0</t>
+          <t>60,18; 69,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,88; 64,04</t>
+          <t>54,04; 63,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,77; 63,24</t>
+          <t>53,53; 62,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 34,44</t>
+          <t>24,19; 34,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 38,36</t>
+          <t>26,4; 37,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,38; 45,81</t>
+          <t>34,92; 46,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,48; 38,4</t>
+          <t>31,07; 38,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,34; 53,38</t>
+          <t>46,53; 53,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,8; 55,49</t>
+          <t>47,44; 55,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,04; 54,46</t>
+          <t>46,83; 54,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,19; 50,44</t>
+          <t>44,41; 50,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,39; 65,08</t>
+          <t>54,3; 65,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,08; 72,9</t>
+          <t>63,47; 73,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,19; 64,71</t>
+          <t>54,02; 64,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,75; 64,82</t>
+          <t>55,04; 64,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 39,37</t>
+          <t>29,8; 39,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 48,55</t>
+          <t>36,36; 48,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,45; 46,07</t>
+          <t>35,42; 46,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,31; 50,13</t>
+          <t>42,39; 50,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,6; 50,68</t>
+          <t>43,55; 50,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,48; 60,62</t>
+          <t>52,58; 60,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,3; 53,82</t>
+          <t>46,3; 54,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,35; 57,31</t>
+          <t>50,34; 57,04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>62,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,68; 70,41</t>
+          <t>62,51; 70,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,16; 76,35</t>
+          <t>68,86; 76,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,32; 69,96</t>
+          <t>61,37; 69,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,02; 93,19</t>
+          <t>63,81; 72,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,52; 52,31</t>
+          <t>37,82; 52,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,34; 67,22</t>
+          <t>54,46; 67,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,84; 66,14</t>
+          <t>50,73; 66,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,4; 52,07</t>
+          <t>40,29; 53,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,71; 64,73</t>
+          <t>57,69; 65,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,08; 72,42</t>
+          <t>66,03; 72,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,48; 67,64</t>
+          <t>60,33; 67,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,57; 90,08</t>
+          <t>58,21; 65,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,4; 66,87</t>
+          <t>61,64; 67,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,29; 71,06</t>
+          <t>65,24; 71,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,87; 69,36</t>
+          <t>63,81; 69,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,14; 71,1</t>
+          <t>64,74; 71,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 47,88</t>
+          <t>40,77; 48,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,96; 54,12</t>
+          <t>46,9; 54,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,12; 50,39</t>
+          <t>43,11; 50,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,53; 79,52</t>
+          <t>48,79; 54,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,64; 58,98</t>
+          <t>54,74; 59,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,87; 63,43</t>
+          <t>58,77; 63,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,1; 60,72</t>
+          <t>56,32; 60,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,74; 75,05</t>
+          <t>58,55; 63,18</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,31; 60,31</t>
+          <t>49,05; 59,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,74; 69,24</t>
+          <t>60,76; 69,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,47; 67,51</t>
+          <t>59,84; 67,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,38; 69,95</t>
+          <t>57,88; 67,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,79; 60,03</t>
+          <t>51,86; 60,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,55; 67,53</t>
+          <t>59,87; 67,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,04; 65,3</t>
+          <t>57,74; 65,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,08; 75,1</t>
+          <t>59,95; 65,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,25; 58,89</t>
+          <t>52,08; 58,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,39; 67,01</t>
+          <t>61,47; 66,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,96; 65,19</t>
+          <t>59,99; 65,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,61; 71,71</t>
+          <t>60,65; 65,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 28,6</t>
+          <t>18,88; 28,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,05; 37,94</t>
+          <t>26,94; 38,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,75; 31,84</t>
+          <t>21,32; 31,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,42; 45,07</t>
+          <t>23,62; 45,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,69; 56,4</t>
+          <t>50,52; 56,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,44; 62,75</t>
+          <t>56,46; 62,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,84; 60,22</t>
+          <t>53,9; 60,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,61; 58,74</t>
+          <t>52,21; 59,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,29; 50,06</t>
+          <t>45,16; 50,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51,38; 56,88</t>
+          <t>51,46; 56,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47,57; 53,22</t>
+          <t>47,43; 53,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,21; 54,24</t>
+          <t>46,75; 54,13</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,52; 60,88</t>
+          <t>57,61; 61,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,56; 67,08</t>
+          <t>63,69; 67,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59,12; 62,58</t>
+          <t>59,07; 62,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,75; 72,68</t>
+          <t>60,32; 63,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,58; 49,0</t>
+          <t>45,66; 49,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,54; 56,16</t>
+          <t>52,63; 56,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,27; 53,99</t>
+          <t>50,48; 53,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,66; 63,74</t>
+          <t>50,54; 53,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,95; 54,41</t>
+          <t>52,02; 54,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58,6; 61,04</t>
+          <t>58,56; 60,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55,21; 57,63</t>
+          <t>55,18; 57,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,34; 66,35</t>
+          <t>55,69; 58,03</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>313447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>150044</t>
+          <t>166364</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>440959</t>
+          <t>479810</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>274944; 319501</t>
+          <t>278526; 321390</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>258991; 300900</t>
+          <t>258680; 300225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>228236; 271260</t>
+          <t>228896; 270201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267323; 314420</t>
+          <t>288310; 336180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71069; 104645</t>
+          <t>73503; 104460</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83811; 119466</t>
+          <t>82212; 117071</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>115461; 153858</t>
+          <t>117262; 154830</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>132778; 167242</t>
+          <t>147748; 185208</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>358385; 412802</t>
+          <t>359864; 414615</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>354302; 411332</t>
+          <t>351702; 410674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>357239; 413583</t>
+          <t>355610; 413273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>412115; 470471</t>
+          <t>450359; 510686</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269081</t>
+          <t>285348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>172373</t>
+          <t>192641</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>441454</t>
+          <t>477989</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>196978; 235670</t>
+          <t>196635; 235763</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>254872; 294546</t>
+          <t>256453; 297140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>198634; 237197</t>
+          <t>198004; 237075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>244441; 289424</t>
+          <t>262296; 307445</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>110033; 145232</t>
+          <t>109935; 146756</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119515; 158534</t>
+          <t>118726; 158112</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>128250; 166676</t>
+          <t>128140; 167419</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>154875; 187962</t>
+          <t>175804; 210459</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>318730; 370478</t>
+          <t>318394; 371543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>383399; 442894</t>
+          <t>384173; 445149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>337230; 391997</t>
+          <t>337239; 396033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>413564; 470709</t>
+          <t>448621; 508305</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532058</t>
+          <t>316784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>84761</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>606286</t>
+          <t>401545</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>339959; 381907</t>
+          <t>339055; 384011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>428280; 472799</t>
+          <t>426457; 474365</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>308444; 351900</t>
+          <t>308669; 350075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>448283; 614138</t>
+          <t>294639; 336573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61782; 86135</t>
+          <t>62274; 86965</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>132902; 164403</t>
+          <t>133199; 164878</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77726; 103148</t>
+          <t>79120; 103576</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63748; 84241</t>
+          <t>73423; 96834</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>408084; 457678</t>
+          <t>407884; 461032</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>570826; 625554</t>
+          <t>570370; 626089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>391904; 445700</t>
+          <t>397509; 446379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>505405; 739422</t>
+          <t>374869; 424525</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>686506</t>
+          <t>753857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>592954</t>
+          <t>436173</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1279461</t>
+          <t>1190031</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>753033; 820119</t>
+          <t>755979; 824900</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>745959; 811953</t>
+          <t>745363; 812318</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>707280; 768034</t>
+          <t>706583; 771688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>651685; 722353</t>
+          <t>719858; 793102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>288633; 339611</t>
+          <t>289171; 341263</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>353599; 407459</t>
+          <t>353128; 407880</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>337887; 394852</t>
+          <t>337853; 393639</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>485503; 764049</t>
+          <t>410403; 461014</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1057722; 1141711</t>
+          <t>1059748; 1147764</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1115826; 1202303</t>
+          <t>1113932; 1203695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1060783; 1148266</t>
+          <t>1064933; 1144019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1180980; 1483614</t>
+          <t>1143601; 1233973</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302895</t>
+          <t>343554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>511745</t>
+          <t>496531</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>814639</t>
+          <t>840085</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>168765; 206438</t>
+          <t>167878; 204559</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>300509; 342567</t>
+          <t>300602; 343321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>349870; 397202</t>
+          <t>352043; 397089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>281125; 325645</t>
+          <t>316608; 367089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>289201; 335224</t>
+          <t>289592; 339223</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>424191; 481025</t>
+          <t>426507; 483235</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>399109; 449060</t>
+          <t>397052; 447580</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>478047; 578319</t>
+          <t>471536; 518691</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>470615; 530415</t>
+          <t>469095; 530732</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>740987; 808819</t>
+          <t>741950; 807723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>765137; 831882</t>
+          <t>765510; 838060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>773626; 886000</t>
+          <t>808821; 873305</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81364</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>397017</t>
+          <t>442184</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>478381</t>
+          <t>519745</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55821; 84794</t>
+          <t>55971; 83874</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71934; 100904</t>
+          <t>71650; 102419</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57593; 88386</t>
+          <t>59188; 88286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57601; 106324</t>
+          <t>54882; 105728</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>621854; 691812</t>
+          <t>619721; 691003</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>594087; 660510</t>
+          <t>594286; 657845</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>540747; 604880</t>
+          <t>541364; 602630</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>370418; 421614</t>
+          <t>416779; 473112</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>689740; 762516</t>
+          <t>687777; 763845</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>677479; 749979</t>
+          <t>678486; 749397</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>609825; 682256</t>
+          <t>608062; 684202</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>440699; 517195</t>
+          <t>481848; 557926</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2162819</t>
+          <t>2090550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1898362</t>
+          <t>1818655</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4061181</t>
+          <t>3909205</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1863126; 1971863</t>
+          <t>1866229; 1975993</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2133197; 2251572</t>
+          <t>2137715; 2251741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1931062; 2044057</t>
+          <t>1929476; 2039816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2050258; 2412984</t>
+          <t>2031758; 2154657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1518579; 1632520</t>
+          <t>1521248; 1639066</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1786480; 1909749</t>
+          <t>1789662; 1909943</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1673720; 1797583</t>
+          <t>1680746; 1795853</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1767122; 2180609</t>
+          <t>1768270; 1874983</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3413555; 3575398</t>
+          <t>3417958; 3583166</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3959546; 4124519</t>
+          <t>3956767; 4118601</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3641429; 3800974</t>
+          <t>3639473; 3806908</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3865037; 4472569</t>
+          <t>3823891; 3984624</t>
         </is>
       </c>
     </row>
